--- a/data_extactor/batch_10_fa/trimmed/batch_0044_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0044_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | درمان و مشاوره | آموزش و تدریس | زیست‌شناسی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | درمان و مشاوره | آموزش و پرورش | زیست‌شناسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان بدنسازی و آمادگی جسمانی | کارشناسان تغذیه و رژیم‌درمانی | مربیان ورزشی و مربیان آمادگی جسمانی گروهی | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپ‌ها | تفریح‌درمانگران | متخصصان پزشکی ورزشی</t>
+          <t>مربیان و متخصصان سلامت و توان‌بخشی ورزشی | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | مربیان ورزش و آمادگی جسمانی گروهی | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | کارشناسان تفریح‌درمانی | پزشکان طب ورزشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | زیست‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | آموزش و پرورش | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کاردرمانگران | فیزیوتراپ‌ها | تفریح‌درمانگران | تنفس‌درمانگران | گفتاردرمانگران | هنر‌درمانگران | موسیقی‌درمانگران</t>
+          <t>کاردرمانگران | فیزیوتراپیست‌ها | کارشناسان تفریح‌درمانی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | هنر‌درمانگران | موسیقی‌درمانگران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | هنرهای تجسمی | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی | آموزش و تدریس</t>
+          <t>درمان و مشاوره | روان‌شناسی | هنرهای زیبا | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | روانی ایده‌ها | ابتکار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و مشاور | ماساژدرمانگران | مشاوران سلامت روان | موسیقی‌درمانگران | کاردرمانگران | تفریح‌درمانگران | گفتاردرمانگران</t>
+          <t>روان‌شناسان بالینی و مشاوران سلامت روان | ماساژدرمانگران | مشاوران سلامت روان | موسیقی‌درمانگران | کاردرمانگران | کارشناسان تفریح‌درمانی | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avid Technology Pro Tools | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار پروتکل صوتی ابزار دیجیتال MIDI | نرم‌افزار سازهای مجازی | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب</t>
+          <t>Avid Technology Pro Tools | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office | نرم‌افزار رابط دیجیتال سازهای موسیقی MIDI | نرم‌افزار ابزار مجازی | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | راهبردهای یادگیری | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | راهبردهای یادگیری | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | هنرهای تجسمی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | آموزش و تدریس</t>
+          <t>درمان و مشاوره | روان‌شناسی | هنرهای زیبا | زبان انگلیسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | توجه شنیداری | حساسیت شنیداری</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | توجه شنیداری | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>هنر‌درمانگران | مدرسان هنر، نمایش و موسیقی در آموزش عالی | روان‌شناسان بالینی و مشاور | رهبران ارکستر و آهنگسازان | کاردرمانگران | تفریح‌درمانگران | گفتاردرمانگران</t>
+          <t>هنر‌درمانگران | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | روان‌شناسان بالینی و مشاوران سلامت روان | رهبران ارکستر، مدیران موسیقی و آهنگسازان | کاردرمانگران | کارشناسان تفریح‌درمانی | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | یادگیری فعال | سخن گفتن | علوم تجربی | تفکر انتقادی | نگارش | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | یادگیری فعال | سخن گفتن | علوم | تفکر انتقادی | نگارش | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | ریاضیات | آموزش و تدریس | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | ریاضیات | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>آسیب‌شناسان (پاتولوژیست‌ها) | متخصصان طب پیشگیری و پزشکی اجتماعی | رادیولوژیست‌ها | کارگران نگهداری حیوانات آزمایشگاهی و کمک‌دامپزشکان | تکنسین‌ها و کارشناسان دامپزشکی</t>
+          <t>پزشکان متخصص پاتولوژی | متخصصان پزشکی اجتماعی و طب پیشگیری | متخصصان رادیولوژی | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>روان‌شناسی | خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | امور اداری و دفتری | درمان و مشاوره | زیست‌شناسی</t>
+          <t>روان‌شناسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | اداری | درمان و مشاوره | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه (ICU/CCU) | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان هوشبری | ماماها | کارشناسان فوریت‌های پزشکی (پارامدیک‌ها)</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران بیهوشی | ماماهای پرستار | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | شنیدن فعال | راهبردهای یادگیری | علوم تجربی | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | گوش دادن فعال | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | روان‌شناسی | درمان و مشاوره | زیست‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | درمان و مشاوره | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه (ICU/CCU) | تکنسین‌های فوریت‌های پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان هوشبری | پرستاران | تنفس‌درمانگران</t>
+          <t>پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران بیهوشی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | پزشکی و دندانپزشکی | زیست‌شناسی | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی</t>
+          <t>روان‌شناسی | درمان و مشاوره | پزشکی و دندان‌پزشکی | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران متخصص بالینی | مشاوران سلامت روان | پرستاران متخصص | بهیاران روانپزشکی | تکنسین‌های روانپزشکی | روانپزشکان | پرستاران</t>
+          <t>پرستاران متخصص بالینی | مشاوران سلامت روان | پرستاران بالینی پیشرفته | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم تجربی</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | روان‌شناسی | زیست‌شناسی | ریاضیات | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | روان‌شناسی | زیست‌شناسی | ریاضیات | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران متخصص بالینی | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان هوشبری | کارشناسان فوریت‌های پزشکی (پارامدیک‌ها) | پرستاران | تنفس‌درمانگران</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران متخصص بالینی | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران بیهوشی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | یادگیری فعال | تفکر انتقادی | درک مطلب | نظارت | شنیدن فعال | نگارش | راهبردهای یادگیری | علوم تجربی</t>
+          <t>سخن گفتن | یادگیری فعال | تفکر انتقادی | درک مطلب | نظارت | گوش دادن فعال | نگارش | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | آموزش و تدریس | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران مراقبت‌های ویژه (ICU/CCU) | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | پرستاران متخصص | دستیاران پزشک | پرستاران</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران مراقبت‌های ویژه | بهیاران و کمک‌پرستاران دارای مجوز | ماماهای پرستار | پرستاران بالینی پیشرفته | دستیاران پزشک | پرستاران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
